--- a/output/pdf_financials_xlsx/CC.xlsx
+++ b/output/pdf_financials_xlsx/CC.xlsx
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.94961</v>
+        <v>-1.94961</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.196155</v>
+        <v>-2.196155</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.94961</v>
+        <v>-1.94961</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.196155</v>
+        <v>-2.196155</v>
       </c>
     </row>
     <row r="24">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>12.185062</v>
+        <v>-12.185062</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>15.686821</v>
+        <v>-15.686821</v>
       </c>
     </row>
     <row r="27">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.95994</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.549126</v>
       </c>
     </row>
     <row r="93">
@@ -2612,7 +2612,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>2.95994</v>
       </c>
@@ -3658,10 +3662,10 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1.94961</v>
+        <v>-1.94961</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>2.196155</v>
+        <v>-2.196155</v>
       </c>
     </row>
     <row r="54">

--- a/output/pdf_financials_xlsx/CC.xlsx
+++ b/output/pdf_financials_xlsx/CC.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.175442</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.047472</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.279142</v>
+        <v>1.1037</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.817682</v>
+        <v>1.77021</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.279142</v>
+        <v>1.1037</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.817682</v>
+        <v>1.77021</v>
       </c>
     </row>
     <row r="30">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">

--- a/output/pdf_financials_xlsx/CC.xlsx
+++ b/output/pdf_financials_xlsx/CC.xlsx
@@ -2778,7 +2778,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.670468</v>
       </c>
